--- a/outputs/Ответы поставщиков.xlsx
+++ b/outputs/Ответы поставщиков.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L178"/>
+  <dimension ref="A1:N184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -444,11 +444,13 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,25 +491,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>FINESKIN, руб</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>J2K, руб</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC, руб</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Лучший</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Лучшая цена, руб</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Наша себестоимость, руб</t>
         </is>
@@ -530,6 +542,8 @@
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -558,18 +572,24 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
+        <v>9020</v>
+      </c>
+      <c r="I3" t="n">
         <v>622</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>622</v>
-      </c>
-      <c r="L3" t="n">
+        <v>615</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>615</v>
+      </c>
+      <c r="N3" t="n">
         <v>664</v>
       </c>
     </row>
@@ -600,18 +620,24 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
+        <v>11900</v>
+      </c>
+      <c r="I4" t="n">
         <v>817</v>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>817</v>
-      </c>
-      <c r="L4" t="n">
+        <v>812</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>812</v>
+      </c>
+      <c r="N4" t="n">
         <v>864</v>
       </c>
     </row>
@@ -642,18 +668,24 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
+        <v>8640</v>
+      </c>
+      <c r="I5" t="n">
         <v>583</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
+        <v>589</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
         <v>583</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>708</v>
       </c>
     </row>
@@ -684,18 +716,24 @@
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
+        <v>11550</v>
+      </c>
+      <c r="I6" t="n">
         <v>772</v>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
+        <v>788</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
         <v>772</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>623</v>
       </c>
     </row>
@@ -726,18 +764,24 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
+        <v>8400</v>
+      </c>
+      <c r="I7" t="n">
         <v>573</v>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>573</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>573</v>
+      </c>
+      <c r="N7" t="n">
         <v>556</v>
       </c>
     </row>
@@ -768,18 +812,24 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
+        <v>12480</v>
+      </c>
+      <c r="I8" t="n">
         <v>872</v>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>872</v>
-      </c>
-      <c r="L8" t="n">
+        <v>851</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>851</v>
+      </c>
+      <c r="N8" t="n">
         <v>688</v>
       </c>
     </row>
@@ -810,18 +860,24 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
+        <v>12180</v>
+      </c>
+      <c r="I9" t="n">
         <v>864</v>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>864</v>
-      </c>
-      <c r="L9" t="n">
+        <v>831</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>831</v>
+      </c>
+      <c r="N9" t="n">
         <v>764</v>
       </c>
     </row>
@@ -852,18 +908,24 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
+        <v>9875</v>
+      </c>
+      <c r="I10" t="n">
         <v>683</v>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>683</v>
-      </c>
-      <c r="L10" t="n">
+        <v>673</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>673</v>
+      </c>
+      <c r="N10" t="n">
         <v>720</v>
       </c>
     </row>
@@ -894,18 +956,24 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
+        <v>11400</v>
+      </c>
+      <c r="I11" t="n">
         <v>759</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
+        <v>777</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>759</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>512</v>
       </c>
     </row>
@@ -936,18 +1004,24 @@
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
+        <v>12480</v>
+      </c>
+      <c r="I12" t="n">
         <v>851</v>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>851</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>851</v>
+      </c>
+      <c r="N12" t="n">
         <v>532</v>
       </c>
     </row>
@@ -968,6 +1042,8 @@
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -995,19 +1071,21 @@
         <v>1781</v>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
         <v>121</v>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
         <v>121</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1035,19 +1113,21 @@
         <v>4431</v>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="n">
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
         <v>302</v>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
         <v>302</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1075,19 +1155,21 @@
         <v>4547</v>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
         <v>310</v>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
         <v>310</v>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1106,6 +1188,8 @@
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1134,18 +1218,24 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
+        <v>3800</v>
+      </c>
+      <c r="I18" t="n">
         <v>223</v>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
+        <v>259</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
         <v>223</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>242</v>
       </c>
     </row>
@@ -1166,6 +1256,8 @@
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1193,19 +1285,21 @@
         <v>2650</v>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="n">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
         <v>181</v>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
         <v>181</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>161</v>
       </c>
     </row>
@@ -1235,19 +1329,21 @@
         <v>2788</v>
       </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
         <v>190</v>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
         <v>190</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>184</v>
       </c>
     </row>
@@ -1277,19 +1373,21 @@
         <v>4240</v>
       </c>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="n">
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
         <v>289</v>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
         <v>289</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1317,19 +1415,21 @@
         <v>4240</v>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="n">
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
         <v>289</v>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
         <v>289</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1357,19 +1457,21 @@
         <v>4240</v>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="n">
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
         <v>289</v>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
         <v>289</v>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1397,19 +1499,21 @@
         <v>3710</v>
       </c>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
         <v>253</v>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
         <v>253</v>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1437,19 +1541,21 @@
         <v>2788</v>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
         <v>190</v>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
         <v>190</v>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1477,19 +1583,21 @@
         <v>3445</v>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
         <v>235</v>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
         <v>235</v>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1517,19 +1625,21 @@
         <v>3445</v>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
         <v>235</v>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
         <v>235</v>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1557,19 +1667,21 @@
         <v>3445</v>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
         <v>235</v>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
         <v>235</v>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1597,19 +1709,21 @@
         <v>3445</v>
       </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="n">
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
         <v>235</v>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
         <v>235</v>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1637,19 +1751,21 @@
         <v>3445</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="n">
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
         <v>235</v>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
         <v>235</v>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1677,19 +1793,21 @@
         <v>3445</v>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
         <v>235</v>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v>235</v>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1717,19 +1835,21 @@
         <v>3445</v>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="n">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
         <v>235</v>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
         <v>235</v>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1757,19 +1877,21 @@
         <v>2523</v>
       </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="n">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
         <v>172</v>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
         <v>172</v>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1797,19 +1919,21 @@
         <v>1728</v>
       </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="n">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
         <v>118</v>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
         <v>118</v>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1837,19 +1961,21 @@
         <v>6890</v>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="n">
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
         <v>470</v>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
         <v>470</v>
       </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1877,19 +2003,21 @@
         <v>6890</v>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="n">
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
         <v>470</v>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
         <v>470</v>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1917,19 +2045,21 @@
         <v>3318</v>
       </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="n">
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
         <v>226</v>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
         <v>226</v>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1957,19 +2087,21 @@
         <v>6233</v>
       </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="n">
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
         <v>425</v>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
         <v>425</v>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1997,19 +2129,21 @@
         <v>6233</v>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="n">
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
         <v>425</v>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
         <v>425</v>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2037,19 +2171,21 @@
         <v>3318</v>
       </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="n">
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
         <v>226</v>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
         <v>226</v>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2077,19 +2213,21 @@
         <v>3318</v>
       </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="n">
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
         <v>226</v>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
         <v>226</v>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2117,19 +2255,21 @@
         <v>3318</v>
       </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="n">
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
         <v>226</v>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
         <v>226</v>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2157,19 +2297,21 @@
         <v>2523</v>
       </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="n">
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
         <v>172</v>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
         <v>172</v>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2197,19 +2339,21 @@
         <v>2788</v>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="n">
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
         <v>190</v>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
         <v>190</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>184</v>
       </c>
     </row>
@@ -2239,19 +2383,21 @@
         <v>3519</v>
       </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="n">
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
         <v>240</v>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
         <v>240</v>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2279,19 +2425,21 @@
         <v>3519</v>
       </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="n">
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
         <v>240</v>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
         <v>240</v>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2319,19 +2467,21 @@
         <v>3519</v>
       </c>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
         <v>240</v>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
         <v>240</v>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2359,19 +2509,21 @@
         <v>6498</v>
       </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="n">
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
         <v>443</v>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
         <v>443</v>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2399,19 +2551,21 @@
         <v>6498</v>
       </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="n">
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
         <v>443</v>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
         <v>443</v>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2439,19 +2593,21 @@
         <v>2385</v>
       </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
         <v>163</v>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
         <v>163</v>
       </c>
-      <c r="L51" t="n">
+      <c r="N51" t="n">
         <v>183</v>
       </c>
     </row>
@@ -2481,19 +2637,21 @@
         <v>2385</v>
       </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="n">
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
         <v>163</v>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
         <v>163</v>
       </c>
-      <c r="L52" t="n">
+      <c r="N52" t="n">
         <v>183</v>
       </c>
     </row>
@@ -2523,19 +2681,21 @@
         <v>2385</v>
       </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="n">
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
         <v>163</v>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
         <v>163</v>
       </c>
-      <c r="L53" t="n">
+      <c r="N53" t="n">
         <v>183</v>
       </c>
     </row>
@@ -2565,19 +2725,21 @@
         <v>4378</v>
       </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
         <v>299</v>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
         <v>299</v>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2605,19 +2767,21 @@
         <v>4378</v>
       </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="n">
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
         <v>299</v>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
         <v>299</v>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2645,19 +2809,21 @@
         <v>4378</v>
       </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="n">
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
         <v>299</v>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
         <v>299</v>
       </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2685,19 +2851,21 @@
         <v>4240</v>
       </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="n">
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
         <v>289</v>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
         <v>289</v>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2725,19 +2893,21 @@
         <v>4240</v>
       </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="n">
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
         <v>289</v>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
         <v>289</v>
       </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2765,19 +2935,21 @@
         <v>4240</v>
       </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="n">
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
         <v>289</v>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
         <v>289</v>
       </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2805,19 +2977,21 @@
         <v>2650</v>
       </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="n">
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
         <v>181</v>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
         <v>181</v>
       </c>
-      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2845,19 +3019,21 @@
         <v>3381</v>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="n">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
         <v>231</v>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
         <v>231</v>
       </c>
-      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2885,25 +3061,27 @@
         <v>3381</v>
       </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
         <v>231</v>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
         <v>231</v>
       </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ETUDE HOUSE</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C63" s="2" t="n"/>
@@ -2916,6 +3094,8 @@
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2923,45 +3103,45 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ETUDE HOUSE</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ET.Baking Powder Pore Scrub 200g(21AD)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>8809820683118</t>
-        </is>
-      </c>
+          <t>ETUDE - Baking Powder Crunch Pore Scrub [200ml]</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>780</v>
-      </c>
-      <c r="F64" t="n">
-        <v>4558</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>311</v>
+        <v>4400</v>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="n">
-        <v>311</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>300</v>
+      </c>
+      <c r="N64" t="n">
+        <v>361</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ETUDE HOUSE</t>
         </is>
       </c>
       <c r="C65" s="2" t="n"/>
@@ -2974,6 +3154,8 @@
       <c r="J65" s="2" t="n"/>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n"/>
+      <c r="N65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2981,87 +3163,65 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
+          <t>ETUDE HOUSE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ET.Baking Powder Pore Scrub 200g(21AD)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>8809820683118</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>780</v>
+      </c>
+      <c r="F66" t="n">
+        <v>4558</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>311</v>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>311</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>FARMSTAY</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>FARMSTAY ARGAN OIL COMPLETE VOLUME UP SHAMPOO &amp; CONDITIONER</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>8809595053659</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>300</v>
-      </c>
-      <c r="F66" t="n">
-        <v>4441</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="n">
-        <v>303</v>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>303</v>
-      </c>
-      <c r="L66" t="n">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>60</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>FARMSTAY</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>FARMSTAY BLACK GARLIC NOURISHING SHAMPOO</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>8809034583617</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>300</v>
-      </c>
-      <c r="F67" t="n">
-        <v>4378</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="n">
-        <v>299</v>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
-        <v>299</v>
-      </c>
-      <c r="L67" t="n">
-        <v>397</v>
-      </c>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n"/>
+      <c r="N67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3070,40 +3230,42 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN PURE CLEANSING FOAM</t>
+          <t>FARMSTAY ARGAN OIL COMPLETE VOLUME UP SHAMPOO &amp; CONDITIONER</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8809317289472</t>
+          <t>8809595053659</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F68" t="n">
-        <v>2311</v>
+        <v>4441</v>
       </c>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="n">
-        <v>158</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K68" t="n">
-        <v>158</v>
-      </c>
-      <c r="L68" t="n">
-        <v>161</v>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>303</v>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>303</v>
+      </c>
+      <c r="N68" t="n">
+        <v>401</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3112,40 +3274,42 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN WATER FULL MOIST CREAM</t>
+          <t>FARMSTAY BLACK GARLIC NOURISHING SHAMPOO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8802221001338</t>
+          <t>8809034583617</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F69" t="n">
-        <v>6911</v>
+        <v>4378</v>
       </c>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="n">
-        <v>471</v>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
-        <v>471</v>
-      </c>
-      <c r="L69" t="n">
-        <v>484</v>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>299</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>299</v>
+      </c>
+      <c r="N69" t="n">
+        <v>397</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3154,40 +3318,42 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN WATER FULL MOIST ROLLING EYE SERUM</t>
+          <t>FARMSTAY COLLAGEN PURE CLEANSING FOAM</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8809480772504</t>
+          <t>8809317289472</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>100</v>
       </c>
       <c r="F70" t="n">
-        <v>3307</v>
+        <v>2311</v>
       </c>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="n">
-        <v>226</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
-        <v>226</v>
-      </c>
-      <c r="L70" t="n">
-        <v>232</v>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>158</v>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>158</v>
+      </c>
+      <c r="N70" t="n">
+        <v>161</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3196,40 +3362,42 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN WATER FULL SHAMPOO &amp; CONDITIONER</t>
+          <t>FARMSTAY COLLAGEN WATER FULL MOIST CREAM</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>8809595053284</t>
+          <t>8802221001338</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F71" t="n">
-        <v>4378</v>
+        <v>6911</v>
       </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="n">
-        <v>299</v>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>299</v>
-      </c>
-      <c r="L71" t="n">
-        <v>397</v>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>471</v>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>471</v>
+      </c>
+      <c r="N71" t="n">
+        <v>484</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3238,40 +3406,42 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
+          <t>FARMSTAY COLLAGEN WATER FULL MOIST ROLLING EYE SERUM</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8800260032009</t>
+          <t>8809480772504</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F72" t="n">
-        <v>5554</v>
+        <v>3307</v>
       </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="n">
-        <v>379</v>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>379</v>
-      </c>
-      <c r="L72" t="n">
-        <v>348</v>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>226</v>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>226</v>
+      </c>
+      <c r="N72" t="n">
+        <v>232</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3280,40 +3450,42 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
+          <t>FARMSTAY COLLAGEN WATER FULL SHAMPOO &amp; CONDITIONER</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8809469772778</t>
+          <t>8809595053284</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="F73" t="n">
-        <v>5554</v>
+        <v>4378</v>
       </c>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="n">
-        <v>379</v>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>379</v>
-      </c>
-      <c r="L73" t="n">
-        <v>390</v>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>299</v>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>299</v>
+      </c>
+      <c r="N73" t="n">
+        <v>397</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3322,96 +3494,126 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
+          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8809317289274</t>
+          <t>8800260032009</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F74" t="n">
-        <v>4791</v>
+        <v>5554</v>
       </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="n">
-        <v>327</v>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
-        <v>327</v>
-      </c>
-      <c r="L74" t="n">
-        <v>314</v>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>379</v>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>379</v>
+      </c>
+      <c r="N74" t="n">
+        <v>348</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
+        <v>67</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FARMSTAY</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>8809469772778</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>80</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5554</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>379</v>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>379</v>
+      </c>
+      <c r="N75" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
         <v>68</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>FARMSTAY</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>FARMSTAY GOLD SNAIL PREMIUM CREAM</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>8809480770975</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>8809317289274</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
         <v>100</v>
       </c>
-      <c r="F75" t="n">
-        <v>7611</v>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="n">
-        <v>519</v>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>519</v>
-      </c>
-      <c r="L75" t="n">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>HEIMISH</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
-      <c r="F76" s="2" t="n"/>
-      <c r="G76" s="2" t="n"/>
-      <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="n"/>
-      <c r="J76" s="2" t="n"/>
-      <c r="K76" s="2" t="n"/>
-      <c r="L76" s="2" t="n"/>
+      <c r="F76" t="n">
+        <v>4791</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>327</v>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>327</v>
+      </c>
+      <c r="N76" t="n">
+        <v>314</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3419,47 +3621,49 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>FARMSTAY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>heimish Artless Glow Base SPF50+ PA+++</t>
+          <t>FARMSTAY GOLD SNAIL PREMIUM CREAM</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>8809481760463</t>
+          <t>8809480770975</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>100</v>
       </c>
       <c r="F77" t="n">
-        <v>10960</v>
+        <v>7611</v>
       </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="n">
-        <v>747</v>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>747</v>
-      </c>
-      <c r="L77" t="n">
-        <v>770</v>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>519</v>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>519</v>
+      </c>
+      <c r="N77" t="n">
+        <v>431</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="C78" s="2" t="n"/>
@@ -3472,6 +3676,8 @@
       <c r="J78" s="2" t="n"/>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n"/>
+      <c r="N78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3479,85 +3685,71 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JIGOTT ALOE REAL AMPOULE MASK</t>
+          <t>heimish Artless Glow Base SPF50+ PA+++</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8809541280269</t>
+          <t>8809481760463</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F79" t="n">
-        <v>159</v>
+        <v>10960</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>11</v>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+        <v>10120</v>
+      </c>
+      <c r="I79" t="n">
+        <v>747</v>
+      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
-        <v>11</v>
-      </c>
-      <c r="L79" t="n">
-        <v>23</v>
+        <v>690</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>690</v>
+      </c>
+      <c r="N79" t="n">
+        <v>770</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>71</v>
-      </c>
-      <c r="B80" t="inlineStr">
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>JIGOTT</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>JIGOTT BIRD'S NEST FIRMING CREAM</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>8809210034087</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>200</v>
-      </c>
-      <c r="F80" t="n">
-        <v>2120</v>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="n">
-        <v>145</v>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>145</v>
-      </c>
-      <c r="L80" t="inlineStr"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n"/>
+      <c r="K80" s="2" t="n"/>
+      <c r="L80" s="2" t="n"/>
+      <c r="M80" s="2" t="n"/>
+      <c r="N80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3566,12 +3758,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JIGOTT BLACK SNAIL REAL AMPOULE MASK</t>
+          <t>JIGOTT ALOE REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8809541280238</t>
+          <t>8809541280269</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -3581,25 +3773,27 @@
         <v>159</v>
       </c>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="n">
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
         <v>11</v>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
         <v>11</v>
       </c>
-      <c r="L81" t="n">
+      <c r="N81" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -3608,40 +3802,40 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JIGOTT CAMELLIA REAL AMPOULE MASK</t>
+          <t>JIGOTT BIRD'S NEST FIRMING CREAM</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8809541280245</t>
+          <t>8809210034087</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F82" t="n">
-        <v>159</v>
+        <v>2120</v>
       </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="n">
-        <v>11</v>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
-        <v>11</v>
-      </c>
-      <c r="L82" t="n">
-        <v>23</v>
-      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>145</v>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>145</v>
+      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3650,12 +3844,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JIGOTT CAVIAR REAL AMPOULE MASK</t>
+          <t>JIGOTT BLACK SNAIL REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>8809541280283</t>
+          <t>8809541280238</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -3665,25 +3859,27 @@
         <v>159</v>
       </c>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="n">
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
         <v>11</v>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
         <v>11</v>
       </c>
-      <c r="L83" t="n">
+      <c r="N83" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3692,12 +3888,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JIGOTT COLLAGEN REAL AMPOULE MASK</t>
+          <t>JIGOTT CAMELLIA REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>8809541280160</t>
+          <t>8809541280245</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -3707,25 +3903,27 @@
         <v>159</v>
       </c>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="n">
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
         <v>11</v>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
         <v>11</v>
       </c>
-      <c r="L84" t="n">
+      <c r="N84" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -3734,12 +3932,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JIGOTT CUCUMBER REAL AMPOULE MASK</t>
+          <t>JIGOTT CAVIAR REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>8809541280146</t>
+          <t>8809541280283</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -3749,25 +3947,27 @@
         <v>159</v>
       </c>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="n">
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
         <v>11</v>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
         <v>11</v>
       </c>
-      <c r="L85" t="n">
+      <c r="N85" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3776,12 +3976,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JIGOTT GREEN TEA REAL AMPOULE MASK</t>
+          <t>JIGOTT COLLAGEN REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>8809541280177</t>
+          <t>8809541280160</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3791,25 +3991,27 @@
         <v>159</v>
       </c>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="n">
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
         <v>11</v>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
         <v>11</v>
       </c>
-      <c r="L86" t="n">
+      <c r="N86" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -3818,12 +4020,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JIGOTT HONEY REAL AMPOULE MASK</t>
+          <t>JIGOTT CUCUMBER REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>8809541280214</t>
+          <t>8809541280146</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3833,25 +4035,27 @@
         <v>159</v>
       </c>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="n">
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
         <v>11</v>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
         <v>11</v>
       </c>
-      <c r="L87" t="n">
+      <c r="N87" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -3860,12 +4064,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>JIGOTT HYALURONIC ACID REAL AMPOULE MASK</t>
+          <t>JIGOTT GREEN TEA REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>8809541280207</t>
+          <t>8809541280177</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3875,25 +4079,27 @@
         <v>159</v>
       </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="n">
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
         <v>11</v>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
         <v>11</v>
       </c>
-      <c r="L88" t="n">
+      <c r="N88" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3902,12 +4108,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JIGOTT LOTUS REAL AMPOULE MASK</t>
+          <t>JIGOTT HONEY REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>8809541280184</t>
+          <t>8809541280214</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -3917,25 +4123,27 @@
         <v>159</v>
       </c>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="n">
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
         <v>11</v>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K89" t="n">
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
         <v>11</v>
       </c>
-      <c r="L89" t="n">
+      <c r="N89" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -3944,12 +4152,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>JIGOTT PEARL REAL AMPOULE MASK</t>
+          <t>JIGOTT HYALURONIC ACID REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>8809541280221</t>
+          <t>8809541280207</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3959,25 +4167,27 @@
         <v>159</v>
       </c>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="n">
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
         <v>11</v>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K90" t="n">
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
         <v>11</v>
       </c>
-      <c r="L90" t="n">
+      <c r="N90" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -3986,12 +4196,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JIGOTT PLACENTA REAL AMPOULE MASK</t>
+          <t>JIGOTT LOTUS REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>8809541280191</t>
+          <t>8809541280184</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -4001,25 +4211,27 @@
         <v>159</v>
       </c>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="n">
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
         <v>11</v>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
         <v>11</v>
       </c>
-      <c r="L91" t="n">
+      <c r="N91" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4028,12 +4240,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JIGOTT POMEGRANATE REAL AMPOULE MASK</t>
+          <t>JIGOTT PEARL REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>8809541280153</t>
+          <t>8809541280221</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -4043,25 +4255,27 @@
         <v>159</v>
       </c>
       <c r="G92" t="inlineStr"/>
-      <c r="H92" t="n">
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="n">
         <v>11</v>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
         <v>11</v>
       </c>
-      <c r="L92" t="n">
+      <c r="N92" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -4070,12 +4284,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JIGOTT POTATO REAL AMPOULE MASK</t>
+          <t>JIGOTT PLACENTA REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>8809541280252</t>
+          <t>8809541280191</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -4085,25 +4299,27 @@
         <v>159</v>
       </c>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="n">
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="n">
         <v>11</v>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
         <v>11</v>
       </c>
-      <c r="L93" t="n">
+      <c r="N93" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -4112,12 +4328,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JIGOTT RED GINSENG REAL AMPOULE MASK</t>
+          <t>JIGOTT POMEGRANATE REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>8809541280276</t>
+          <t>8809541280153</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -4127,25 +4343,27 @@
         <v>159</v>
       </c>
       <c r="G94" t="inlineStr"/>
-      <c r="H94" t="n">
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="n">
         <v>11</v>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
         <v>11</v>
       </c>
-      <c r="L94" t="n">
+      <c r="N94" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -4154,40 +4372,42 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JIGOTT SNAIL LIFTING CREAM</t>
+          <t>JIGOTT POTATO REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>8809210034124</t>
+          <t>8809541280252</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F95" t="n">
-        <v>2120</v>
+        <v>159</v>
       </c>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="n">
-        <v>145</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>145</v>
-      </c>
-      <c r="L95" t="n">
-        <v>202</v>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>11</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>11</v>
+      </c>
+      <c r="N95" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -4196,40 +4416,42 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JIGOTT SNAIL REPARING CREAM</t>
+          <t>JIGOTT RED GINSENG REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>8809210036517</t>
+          <t>8809541280276</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="F96" t="n">
-        <v>2120</v>
+        <v>159</v>
       </c>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="n">
-        <v>145</v>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>145</v>
-      </c>
-      <c r="L96" t="n">
-        <v>186</v>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>11</v>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>11</v>
+      </c>
+      <c r="N96" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4238,40 +4460,42 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JIGOTT VITAMIN REAL AMPOULE MASK</t>
+          <t>JIGOTT SNAIL LIFTING CREAM</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>8809541280139</t>
+          <t>8809210034124</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="F97" t="n">
-        <v>159</v>
+        <v>2120</v>
       </c>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="n">
-        <v>11</v>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K97" t="n">
-        <v>11</v>
-      </c>
-      <c r="L97" t="n">
-        <v>23</v>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>145</v>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>145</v>
+      </c>
+      <c r="N97" t="n">
+        <v>202</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -4280,40 +4504,42 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jigott Daily Real Cica Toner</t>
+          <t>JIGOTT SNAIL REPARING CREAM</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>8809541282447</t>
+          <t>8809210036517</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F98" t="n">
         <v>2120</v>
       </c>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="n">
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
         <v>145</v>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K98" t="n">
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
         <v>145</v>
       </c>
-      <c r="L98" t="n">
-        <v>265</v>
+      <c r="N98" t="n">
+        <v>186</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -4322,40 +4548,42 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jigott Moisture Real Aloe Vera Toner</t>
+          <t>JIGOTT VITAMIN REAL AMPOULE MASK</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>8809541282508</t>
+          <t>8809541280139</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F99" t="n">
-        <v>2120</v>
+        <v>159</v>
       </c>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="n">
-        <v>145</v>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K99" t="n">
-        <v>145</v>
-      </c>
-      <c r="L99" t="n">
-        <v>265</v>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>11</v>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>11</v>
+      </c>
+      <c r="N99" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -4364,12 +4592,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jigott Ultimate Real Collagen Toner</t>
+          <t>Jigott Daily Real Cica Toner</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>8809541282461</t>
+          <t>8809541282447</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -4379,39 +4607,67 @@
         <v>2120</v>
       </c>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="n">
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="n">
         <v>145</v>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
         <v>145</v>
       </c>
-      <c r="L100" t="n">
+      <c r="N100" t="n">
         <v>265</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n"/>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="2" t="n"/>
-      <c r="G101" s="2" t="n"/>
-      <c r="H101" s="2" t="n"/>
-      <c r="I101" s="2" t="n"/>
-      <c r="J101" s="2" t="n"/>
-      <c r="K101" s="2" t="n"/>
-      <c r="L101" s="2" t="n"/>
+      <c r="A101" t="n">
+        <v>91</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Jigott Moisture Real Aloe Vera Toner</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>8809541282508</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>145</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>145</v>
+      </c>
+      <c r="N101" t="n">
+        <v>265</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4419,85 +4675,67 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>JIGOTT</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Jigott Ultimate Real Collagen Toner</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>8809541282461</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2120</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>145</v>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>145</v>
+      </c>
+      <c r="N102" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>JMSOLUTION</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>JMSOLUTION ACTIVE BIRDS' NEST MOISTURE MASK PRIME</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>8809505547667</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>80</v>
-      </c>
-      <c r="F102" t="n">
-        <v>3604</v>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="n">
-        <v>246</v>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>246</v>
-      </c>
-      <c r="L102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>93</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>JMSOLUTION</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>8809696353658</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>80</v>
-      </c>
-      <c r="F103" t="n">
-        <v>3604</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="n">
-        <v>246</v>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K103" t="n">
-        <v>246</v>
-      </c>
-      <c r="L103" t="n">
-        <v>342</v>
-      </c>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+      <c r="J103" s="2" t="n"/>
+      <c r="K103" s="2" t="n"/>
+      <c r="L103" s="2" t="n"/>
+      <c r="M103" s="2" t="n"/>
+      <c r="N103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -4506,12 +4744,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JMSOLUTION ACTIVE GOLDEN CAVIAR NOURISHING MASK PRIME</t>
+          <t>JMSOLUTION ACTIVE BIRDS' NEST MOISTURE MASK PRIME</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>8809505547698</t>
+          <t>8809505547667</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -4521,23 +4759,25 @@
         <v>3604</v>
       </c>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="n">
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="n">
         <v>246</v>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K104" t="n">
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
         <v>246</v>
       </c>
-      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -4546,12 +4786,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>JMSOLUTION ACTIVE JELLYFISH VITAL MASK PRIME</t>
+          <t>JMSOLUTION ACTIVE BLACK CAVIAR MASK</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>8809505547636</t>
+          <t>8809696353658</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -4561,23 +4801,27 @@
         <v>3604</v>
       </c>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="n">
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="n">
         <v>246</v>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K105" t="n">
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
         <v>246</v>
       </c>
-      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="n">
+        <v>342</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -4586,40 +4830,40 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
+          <t>JMSOLUTION ACTIVE GOLDEN CAVIAR NOURISHING MASK PRIME</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>8809711711531</t>
+          <t>8809505547698</t>
         </is>
       </c>
       <c r="E106" t="n">
         <v>80</v>
       </c>
       <c r="F106" t="n">
-        <v>5311</v>
+        <v>3604</v>
       </c>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="n">
-        <v>362</v>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K106" t="n">
-        <v>362</v>
-      </c>
-      <c r="L106" t="n">
-        <v>450</v>
-      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="n">
+        <v>246</v>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>246</v>
+      </c>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -4628,40 +4872,40 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JMSOLUTION GLORY AQUA TOCOPHEROL VITAMIN C MASK PLUS</t>
+          <t>JMSOLUTION ACTIVE JELLYFISH VITAL MASK PRIME</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>8809794737022</t>
+          <t>8809505547636</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>80</v>
       </c>
       <c r="F107" t="n">
-        <v>5311</v>
+        <v>3604</v>
       </c>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="n">
-        <v>362</v>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
-        <v>362</v>
-      </c>
-      <c r="L107" t="n">
-        <v>450</v>
-      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>246</v>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>246</v>
+      </c>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4670,40 +4914,42 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea</t>
+          <t>JMSOLUTION GLORY AQUA FULLERENE MASK DELUXE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>8809696354129</t>
+          <t>8809711711531</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>80</v>
       </c>
       <c r="F108" t="n">
-        <v>3604</v>
+        <v>5311</v>
       </c>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="n">
-        <v>246</v>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
-        <v>246</v>
-      </c>
-      <c r="L108" t="n">
-        <v>342</v>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="n">
+        <v>362</v>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>362</v>
+      </c>
+      <c r="N108" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4712,12 +4958,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+          <t>JMSOLUTION GLORY AQUA TOCOPHEROL VITAMIN C MASK PLUS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>8809711712491</t>
+          <t>8809794737022</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -4727,25 +4973,27 @@
         <v>5311</v>
       </c>
       <c r="G109" t="inlineStr"/>
-      <c r="H109" t="n">
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="n">
         <v>362</v>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K109" t="n">
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
         <v>362</v>
       </c>
-      <c r="L109" t="n">
+      <c r="N109" t="n">
         <v>450</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4754,12 +5002,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>JMSOLUTION THE NATURAL CORDYCEPS MILITARIS MASK MOISTURE</t>
+          <t>JMSOLUTION GREEN DEAR TIGER CICA MASK PURE 30ml*10ea</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>8809852542087</t>
+          <t>8809696354129</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -4769,37 +5017,67 @@
         <v>3604</v>
       </c>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="n">
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="n">
         <v>246</v>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
         <v>246</v>
       </c>
-      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="n">
+        <v>342</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n"/>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>LANEIGE</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n"/>
-      <c r="E111" s="2" t="n"/>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="2" t="n"/>
-      <c r="H111" s="2" t="n"/>
-      <c r="I111" s="2" t="n"/>
-      <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
-      <c r="L111" s="2" t="n"/>
+      <c r="A111" t="n">
+        <v>100</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>JMSOLUTION PANTHELENE INTENSIVE BARRIER MASK</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>8809711712491</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>80</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5311</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="n">
+        <v>362</v>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>362</v>
+      </c>
+      <c r="N111" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -4807,83 +5085,65 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>JMSOLUTION</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>JMSOLUTION THE NATURAL CORDYCEPS MILITARIS MASK MOISTURE</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>8809852542087</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>80</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3604</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="n">
+        <v>246</v>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>246</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>LANEIGE</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>LIP SLEEPING MASK EX [APPLE LIME] 20g</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>8809685797371</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>100</v>
-      </c>
-      <c r="F112" t="n">
-        <v>11236</v>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="n">
-        <v>766</v>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K112" t="n">
-        <v>766</v>
-      </c>
-      <c r="L112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>102</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>LANEIGE</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>LIP SLEEPING MASK EX [BERRY] 20g</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>8809685797173</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>200</v>
-      </c>
-      <c r="F113" t="n">
-        <v>11236</v>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="n">
-        <v>766</v>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K113" t="n">
-        <v>766</v>
-      </c>
-      <c r="L113" t="inlineStr"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
+      <c r="J113" s="2" t="n"/>
+      <c r="K113" s="2" t="n"/>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" s="2" t="n"/>
+      <c r="N113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -4892,34 +5152,40 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [BERRY] 3g</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>LIP SLEEPING MASK EX [APPLE LIME] 20g</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>8809685797371</t>
+        </is>
+      </c>
       <c r="E114" t="n">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="F114" t="n">
-        <v>2207</v>
+        <v>11236</v>
       </c>
       <c r="G114" t="inlineStr"/>
-      <c r="H114" t="n">
-        <v>151</v>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K114" t="n">
-        <v>151</v>
-      </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="n">
+        <v>766</v>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>766</v>
+      </c>
+      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -4928,38 +5194,40 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [GRAPEFRUIT] 20g</t>
+          <t>LIP SLEEPING MASK EX [BERRY] 20g</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>8809685797357</t>
+          <t>8809685797173</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F115" t="n">
         <v>11236</v>
       </c>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="n">
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="n">
         <v>766</v>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K115" t="n">
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
         <v>766</v>
       </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -4968,38 +5236,36 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [GUMMY BEAR] 20g</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>8809925206427</t>
-        </is>
-      </c>
+          <t>LIP SLEEPING MASK EX [BERRY] 3g</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="F116" t="n">
-        <v>12084</v>
+        <v>2207</v>
       </c>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="n">
-        <v>824</v>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K116" t="n">
-        <v>824</v>
-      </c>
-      <c r="L116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>151</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>151</v>
+      </c>
+      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -5008,34 +5274,40 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [GUMMY BEAR] 3g</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>LIP SLEEPING MASK EX [GRAPEFRUIT] 20g</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>8809685797357</t>
+        </is>
+      </c>
       <c r="E117" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="F117" t="n">
-        <v>2313</v>
+        <v>11236</v>
       </c>
       <c r="G117" t="inlineStr"/>
-      <c r="H117" t="n">
-        <v>158</v>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K117" t="n">
-        <v>158</v>
-      </c>
-      <c r="L117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>766</v>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>766</v>
+      </c>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -5044,12 +5316,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [MANGO] 20g</t>
+          <t>LIP SLEEPING MASK EX [GUMMY BEAR] 20g</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>8809925206410</t>
+          <t>8809925206427</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -5059,23 +5331,25 @@
         <v>12084</v>
       </c>
       <c r="G118" t="inlineStr"/>
-      <c r="H118" t="n">
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="n">
         <v>824</v>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K118" t="n">
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
         <v>824</v>
       </c>
-      <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -5084,7 +5358,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [MANGO] 3g</t>
+          <t>LIP SLEEPING MASK EX [GUMMY BEAR] 3g</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -5092,26 +5366,28 @@
         <v>2000</v>
       </c>
       <c r="F119" t="n">
-        <v>2631</v>
+        <v>2313</v>
       </c>
       <c r="G119" t="inlineStr"/>
-      <c r="H119" t="n">
-        <v>179</v>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K119" t="n">
-        <v>179</v>
-      </c>
-      <c r="L119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>158</v>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>158</v>
+      </c>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -5120,38 +5396,40 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [MINT CHOCO] 20g</t>
+          <t>LIP SLEEPING MASK EX [MANGO] 20g</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>8809685797395</t>
+          <t>8809925206410</t>
         </is>
       </c>
       <c r="E120" t="n">
         <v>100</v>
       </c>
       <c r="F120" t="n">
-        <v>11236</v>
+        <v>12084</v>
       </c>
       <c r="G120" t="inlineStr"/>
-      <c r="H120" t="n">
-        <v>766</v>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K120" t="n">
-        <v>766</v>
-      </c>
-      <c r="L120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="n">
+        <v>824</v>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
+        <v>824</v>
+      </c>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -5160,38 +5438,36 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [PEACH ICED TEA] 20g</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>8809925206441</t>
-        </is>
-      </c>
+          <t>LIP SLEEPING MASK EX [MANGO] 3g</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="F121" t="n">
-        <v>12084</v>
+        <v>2631</v>
       </c>
       <c r="G121" t="inlineStr"/>
-      <c r="H121" t="n">
-        <v>824</v>
-      </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K121" t="n">
-        <v>824</v>
-      </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>179</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>179</v>
+      </c>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -5200,38 +5476,40 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [SWEET CANDY] 20g</t>
+          <t>LIP SLEEPING MASK EX [MINT CHOCO] 20g</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>8809925206433</t>
+          <t>8809685797395</t>
         </is>
       </c>
       <c r="E122" t="n">
         <v>100</v>
       </c>
       <c r="F122" t="n">
-        <v>12084</v>
+        <v>11236</v>
       </c>
       <c r="G122" t="inlineStr"/>
-      <c r="H122" t="n">
-        <v>824</v>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K122" t="n">
-        <v>824</v>
-      </c>
-      <c r="L122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>766</v>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M122" t="n">
+        <v>766</v>
+      </c>
+      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -5240,34 +5518,40 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [SWEET CANDY] 3g</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t>LIP SLEEPING MASK EX [PEACH ICED TEA] 20g</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>8809925206441</t>
+        </is>
+      </c>
       <c r="E123" t="n">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="F123" t="n">
-        <v>2631</v>
+        <v>12084</v>
       </c>
       <c r="G123" t="inlineStr"/>
-      <c r="H123" t="n">
-        <v>179</v>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K123" t="n">
-        <v>179</v>
-      </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>824</v>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>824</v>
+      </c>
+      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -5276,92 +5560,116 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LIP SLEEPING MASK EX [Strawberry cake] 20g</t>
+          <t>LIP SLEEPING MASK EX [SWEET CANDY] 20g</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>8800283633894</t>
+          <t>8809925206433</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F124" t="n">
-        <v>12633</v>
+        <v>12084</v>
       </c>
       <c r="G124" t="inlineStr"/>
-      <c r="H124" t="n">
-        <v>862</v>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K124" t="n">
-        <v>862</v>
-      </c>
-      <c r="L124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>824</v>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
+        <v>824</v>
+      </c>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
+        <v>113</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>LANEIGE</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>LIP SLEEPING MASK EX [SWEET CANDY] 3g</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2631</v>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>179</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>179</v>
+      </c>
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
         <v>114</v>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>LANEIGE</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>LIP SLEEPING MASK EX [VANILLA] 20g</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>8809925203808</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>100</v>
-      </c>
-      <c r="F125" t="n">
-        <v>12084</v>
-      </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="n">
-        <v>824</v>
-      </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K125" t="n">
-        <v>824</v>
-      </c>
-      <c r="L125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n"/>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>LEBELAGE</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n"/>
-      <c r="E126" s="2" t="n"/>
-      <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="n"/>
-      <c r="J126" s="2" t="n"/>
-      <c r="K126" s="2" t="n"/>
-      <c r="L126" s="2" t="n"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>LIP SLEEPING MASK EX [Strawberry cake] 20g</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>8800283633894</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>200</v>
+      </c>
+      <c r="F126" t="n">
+        <v>12633</v>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="n">
+        <v>862</v>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M126" t="n">
+        <v>862</v>
+      </c>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5369,47 +5677,47 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>LANEIGE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LEBELAGE Dr. PEPTIDE DERMA EYE CREAM</t>
+          <t>LIP SLEEPING MASK EX [VANILLA] 20g</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>8809445616553</t>
+          <t>8809925203808</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F127" t="n">
-        <v>1431</v>
+        <v>12084</v>
       </c>
       <c r="G127" t="inlineStr"/>
-      <c r="H127" t="n">
-        <v>98</v>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K127" t="n">
-        <v>98</v>
-      </c>
-      <c r="L127" t="n">
-        <v>108</v>
-      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="n">
+        <v>824</v>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>824</v>
+      </c>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>MANYO FACTORY</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="C128" s="2" t="n"/>
@@ -5422,6 +5730,8 @@
       <c r="J128" s="2" t="n"/>
       <c r="K128" s="2" t="n"/>
       <c r="L128" s="2" t="n"/>
+      <c r="M128" s="2" t="n"/>
+      <c r="N128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -5429,137 +5739,145 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MANYO FACTORY</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ma:nyo BIFIDA BIOME AMPOULE LOTION 300ML</t>
+          <t>LEBELAGE Dr. PEPTIDE DERMA EYE CREAM</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>8809730952236</t>
+          <t>8809445616553</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F129" t="n">
-        <v>9540</v>
+        <v>1431</v>
       </c>
       <c r="G129" t="inlineStr"/>
-      <c r="H129" t="n">
-        <v>651</v>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K129" t="n">
-        <v>651</v>
-      </c>
-      <c r="L129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="n">
+        <v>98</v>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M129" t="n">
+        <v>98</v>
+      </c>
+      <c r="N129" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
-        <v>117</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>MANYO FACTORY</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>ma:nyo BIFIDA BIOME COMPLEX AMPOULE 50ML</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>8809657114700</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F130" t="n">
-        <v>13356</v>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="n">
-        <v>911</v>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K130" t="n">
-        <v>911</v>
-      </c>
-      <c r="L130" t="inlineStr"/>
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+      <c r="J130" s="2" t="n"/>
+      <c r="K130" s="2" t="n"/>
+      <c r="L130" s="2" t="n"/>
+      <c r="M130" s="2" t="n"/>
+      <c r="N130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MANYO FACTORY</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ma:nyo BIFIDA COMPLEX AMPOULE GEL CLEANSER 400ML</t>
+          <t>MANYO - Galac Whitening Vita Serum [50ml]</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>8809567929722</t>
+          <t>8809730952014</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>700</v>
-      </c>
-      <c r="F131" t="n">
-        <v>8777</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>599</v>
+        <v>9500</v>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="n">
-        <v>599</v>
-      </c>
-      <c r="L131" t="inlineStr"/>
+        <v>648</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
+        <v>648</v>
+      </c>
+      <c r="N131" t="n">
+        <v>647</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n"/>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n"/>
-      <c r="E132" s="2" t="n"/>
-      <c r="F132" s="2" t="n"/>
-      <c r="G132" s="2" t="n"/>
-      <c r="H132" s="2" t="n"/>
-      <c r="I132" s="2" t="n"/>
-      <c r="J132" s="2" t="n"/>
-      <c r="K132" s="2" t="n"/>
-      <c r="L132" s="2" t="n"/>
+      <c r="A132" t="n">
+        <v>118</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>MANYO</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MANYO - Pure Cleansing Oil [200ml] (discontinued)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="n">
+        <v>80</v>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="n">
+        <v>9500</v>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="n">
+        <v>648</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M132" t="n">
+        <v>648</v>
+      </c>
+      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -5567,231 +5885,225 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>8809730957705</t>
+        </is>
+      </c>
       <c r="E133" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="n">
-        <v>6190</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="n">
-        <v>422</v>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>J2K</t>
-        </is>
-      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>14820</v>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="n">
-        <v>422</v>
-      </c>
-      <c r="L133" t="n">
-        <v>415</v>
+        <v>1011</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M133" t="n">
+        <v>1011</v>
+      </c>
+      <c r="N133" t="n">
+        <v>997</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
-        <v>120</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="n">
-        <v>200</v>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="n">
-        <v>6190</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="n">
-        <v>422</v>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>J2K</t>
-        </is>
-      </c>
-      <c r="K134" t="n">
-        <v>422</v>
-      </c>
-      <c r="L134" t="n">
-        <v>415</v>
-      </c>
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>MANYO FACTORY</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="2" t="n"/>
+      <c r="I134" s="2" t="n"/>
+      <c r="J134" s="2" t="n"/>
+      <c r="K134" s="2" t="n"/>
+      <c r="L134" s="2" t="n"/>
+      <c r="M134" s="2" t="n"/>
+      <c r="N134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO FACTORY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>ma:nyo BIFIDA BIOME AMPOULE LOTION 300ML</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>8809730952236</t>
+        </is>
+      </c>
       <c r="E135" t="n">
-        <v>100</v>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="n">
-        <v>8180</v>
-      </c>
-      <c r="H135" t="inlineStr"/>
+        <v>600</v>
+      </c>
+      <c r="F135" t="n">
+        <v>9540</v>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>9500</v>
+      </c>
       <c r="I135" t="n">
-        <v>558</v>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>J2K</t>
-        </is>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="n">
-        <v>558</v>
-      </c>
-      <c r="L135" t="n">
-        <v>591</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M135" t="n">
+        <v>648</v>
+      </c>
+      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MANYO FACTORY</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
+          <t>ma:nyo BIFIDA BIOME COMPLEX AMPOULE 50ML</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>8809657114700</t>
+        </is>
+      </c>
       <c r="E136" t="n">
-        <v>200</v>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="n">
-        <v>6790</v>
-      </c>
-      <c r="H136" t="inlineStr"/>
+        <v>1400</v>
+      </c>
+      <c r="F136" t="n">
+        <v>13356</v>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="n">
+        <v>8740</v>
+      </c>
       <c r="I136" t="n">
-        <v>463</v>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>J2K</t>
-        </is>
-      </c>
+        <v>911</v>
+      </c>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="n">
-        <v>463</v>
-      </c>
-      <c r="L136" t="n">
-        <v>487</v>
-      </c>
+        <v>596</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M136" t="n">
+        <v>596</v>
+      </c>
+      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
+          <t>MANYO FACTORY</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ma:nyo BIFIDA COMPLEX AMPOULE GEL CLEANSER 400ML</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>8809567929722</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>700</v>
+      </c>
+      <c r="F137" t="n">
+        <v>8777</v>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="n">
+        <v>8740</v>
+      </c>
+      <c r="I137" t="n">
+        <v>599</v>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>596</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M137" t="n">
+        <v>596</v>
+      </c>
+      <c r="N137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n"/>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>PETITFEE</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="n">
-        <v>300</v>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="n">
-        <v>820</v>
-      </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="n">
-        <v>56</v>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>J2K</t>
-        </is>
-      </c>
-      <c r="K137" t="n">
-        <v>56</v>
-      </c>
-      <c r="L137" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>124</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>PETITFEE</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea]</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="n">
-        <v>100</v>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="n">
-        <v>6190</v>
-      </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="n">
-        <v>422</v>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>J2K</t>
-        </is>
-      </c>
-      <c r="K138" t="n">
-        <v>422</v>
-      </c>
-      <c r="L138" t="n">
-        <v>415</v>
-      </c>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="2" t="n"/>
+      <c r="H138" s="2" t="n"/>
+      <c r="I138" s="2" t="n"/>
+      <c r="J138" s="2" t="n"/>
+      <c r="K138" s="2" t="n"/>
+      <c r="L138" s="2" t="n"/>
+      <c r="M138" s="2" t="n"/>
+      <c r="N138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5800,36 +6112,38 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>7290</v>
+        <v>6190</v>
       </c>
       <c r="H139" t="inlineStr"/>
-      <c r="I139" t="n">
-        <v>497</v>
-      </c>
-      <c r="J139" t="inlineStr">
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="n">
+        <v>422</v>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K139" t="n">
-        <v>497</v>
-      </c>
-      <c r="L139" t="n">
-        <v>497</v>
+      <c r="M139" t="n">
+        <v>422</v>
+      </c>
+      <c r="N139" t="n">
+        <v>415</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -5838,36 +6152,38 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea]</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
         <v>6190</v>
       </c>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="n">
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="n">
         <v>422</v>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K140" t="n">
+      <c r="M140" t="n">
         <v>422</v>
       </c>
-      <c r="L140" t="n">
+      <c r="N140" t="n">
         <v>415</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -5876,34 +6192,38 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs]</t>
+          <t>PETITFEE - Aura Quartz Hydrogel Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>820</v>
+        <v>8180</v>
       </c>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="n">
-        <v>56</v>
-      </c>
-      <c r="J141" t="inlineStr">
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="n">
+        <v>558</v>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K141" t="n">
-        <v>56</v>
-      </c>
-      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>558</v>
+      </c>
+      <c r="N141" t="n">
+        <v>591</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -5912,36 +6232,38 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea]</t>
+          <t>PETITFEE - Bera Glucan Deep Firming Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
         <v>6790</v>
       </c>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="n">
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="n">
         <v>463</v>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K142" t="n">
+      <c r="M142" t="n">
         <v>463</v>
       </c>
-      <c r="L142" t="n">
+      <c r="N142" t="n">
         <v>487</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -5950,38 +6272,38 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PETITFEE AGAVE COOLING EYE MASK</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>8809508850429</t>
-        </is>
-      </c>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Eye Patch [1 pairs]</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>360</v>
-      </c>
-      <c r="F143" t="n">
-        <v>6264</v>
-      </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="n">
-        <v>427</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="n">
+        <v>820</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K143" t="n">
-        <v>427</v>
-      </c>
-      <c r="L143" t="inlineStr"/>
+      <c r="J143" t="n">
+        <v>56</v>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>J2K</t>
+        </is>
+      </c>
+      <c r="M143" t="n">
+        <v>56</v>
+      </c>
+      <c r="N143" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -5990,44 +6312,38 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PETITFEE AGAVE COOLING FACE MASK</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>8809508850450</t>
-        </is>
-      </c>
+          <t>PETITFEE - Cacao Energizing Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="n">
-        <v>600</v>
-      </c>
-      <c r="F144" t="n">
-        <v>7324</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>7290</v>
-      </c>
-      <c r="H144" t="n">
-        <v>499</v>
-      </c>
-      <c r="I144" t="n">
-        <v>497</v>
-      </c>
-      <c r="J144" t="inlineStr">
+        <v>6190</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="n">
+        <v>422</v>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K144" t="n">
-        <v>497</v>
-      </c>
-      <c r="L144" t="n">
-        <v>486</v>
+      <c r="M144" t="n">
+        <v>422</v>
+      </c>
+      <c r="N144" t="n">
+        <v>415</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -6036,38 +6352,38 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>PETITFEE ARTICHOKE SOOTHING HYDROGEL EYE MASK</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>8809508850559</t>
-        </is>
-      </c>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>216</v>
-      </c>
-      <c r="F145" t="n">
-        <v>6264</v>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="n">
-        <v>427</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="n">
+        <v>7290</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K145" t="n">
-        <v>427</v>
-      </c>
-      <c r="L145" t="inlineStr"/>
+      <c r="J145" t="n">
+        <v>497</v>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>J2K</t>
+        </is>
+      </c>
+      <c r="M145" t="n">
+        <v>497</v>
+      </c>
+      <c r="N145" t="n">
+        <v>497</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -6076,44 +6392,38 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PETITFEE ARTICHOKE SOOTHING HYDROGEL FACE MASK</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>8809508850566</t>
-        </is>
-      </c>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
-        <v>90</v>
-      </c>
-      <c r="F146" t="n">
-        <v>7324</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>7290</v>
-      </c>
-      <c r="H146" t="n">
-        <v>499</v>
-      </c>
-      <c r="I146" t="n">
-        <v>497</v>
-      </c>
-      <c r="J146" t="inlineStr">
+        <v>6190</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="n">
+        <v>422</v>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K146" t="n">
-        <v>497</v>
-      </c>
-      <c r="L146" t="n">
-        <v>499</v>
+      <c r="M146" t="n">
+        <v>422</v>
+      </c>
+      <c r="N146" t="n">
+        <v>415</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -6122,38 +6432,36 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PETITFEE B-GLUCAN DEEP FIRMING EYE MASK</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>8809508850504</t>
-        </is>
-      </c>
+          <t>PETITFEE - Gold Hydrogel Eye Patch [1 Pairs]</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>180</v>
-      </c>
-      <c r="F147" t="n">
-        <v>6842</v>
-      </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="n">
-        <v>467</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="n">
+        <v>820</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K147" t="n">
-        <v>467</v>
-      </c>
-      <c r="L147" t="inlineStr"/>
+      <c r="J147" t="n">
+        <v>56</v>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>J2K</t>
+        </is>
+      </c>
+      <c r="M147" t="n">
+        <v>56</v>
+      </c>
+      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -6162,42 +6470,38 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PETITFEE BLACK PEARL &amp; GOLD HYDROGEL EYE PATCH</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>8809239801820</t>
-        </is>
-      </c>
+          <t>PETITFEE - Pink Vita Brightening Eye Patch [60ea]</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
-        <v>216</v>
-      </c>
-      <c r="F148" t="n">
-        <v>5782</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>5690</v>
-      </c>
-      <c r="H148" t="n">
-        <v>394</v>
-      </c>
-      <c r="I148" t="n">
-        <v>388</v>
-      </c>
-      <c r="J148" t="inlineStr">
+        <v>6790</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="n">
+        <v>463</v>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K148" t="n">
-        <v>388</v>
-      </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="n">
+        <v>463</v>
+      </c>
+      <c r="N148" t="n">
+        <v>487</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -6206,38 +6510,40 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PETITFEE BLACK PEARL &amp; GOLD HYDROGEL EYE PATCH 1EA</t>
+          <t>PETITFEE AGAVE COOLING EYE MASK</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>8809508850597</t>
+          <t>8809508850429</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>440</v>
+        <v>360</v>
       </c>
       <c r="F149" t="n">
-        <v>819</v>
+        <v>6264</v>
       </c>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" t="n">
-        <v>56</v>
-      </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K149" t="n">
-        <v>56</v>
-      </c>
-      <c r="L149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="n">
+        <v>427</v>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
+        <v>427</v>
+      </c>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -6246,44 +6552,46 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PETITFEE BLACK PEARL &amp; GOLD HYDROGEL MASK PACK</t>
+          <t>PETITFEE AGAVE COOLING FACE MASK</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>8809508850191</t>
+          <t>8809508850450</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="F150" t="n">
-        <v>7035</v>
+        <v>7324</v>
       </c>
       <c r="G150" t="n">
-        <v>6990</v>
-      </c>
-      <c r="H150" t="n">
-        <v>480</v>
-      </c>
+        <v>7290</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
       <c r="I150" t="n">
-        <v>477</v>
-      </c>
-      <c r="J150" t="inlineStr">
+        <v>499</v>
+      </c>
+      <c r="J150" t="n">
+        <v>497</v>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K150" t="n">
-        <v>477</v>
-      </c>
-      <c r="L150" t="n">
-        <v>478</v>
+      <c r="M150" t="n">
+        <v>497</v>
+      </c>
+      <c r="N150" t="n">
+        <v>486</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -6292,38 +6600,40 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PETITFEE CACAO ENERGIZING HYDROGEL EYE MASK</t>
+          <t>PETITFEE ARTICHOKE SOOTHING HYDROGEL EYE MASK</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>8809508850696</t>
+          <t>8809508850559</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>72</v>
+        <v>216</v>
       </c>
       <c r="F151" t="n">
         <v>6264</v>
       </c>
       <c r="G151" t="inlineStr"/>
-      <c r="H151" t="n">
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="n">
         <v>427</v>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K151" t="n">
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
         <v>427</v>
       </c>
-      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -6332,12 +6642,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PETITFEE CACAO ENERGIZING HYDROGEL FACE MASK</t>
+          <t>PETITFEE ARTICHOKE SOOTHING HYDROGEL FACE MASK</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>8809508850689</t>
+          <t>8809508850566</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -6346,24 +6656,32 @@
       <c r="F152" t="n">
         <v>7324</v>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="n">
+      <c r="G152" t="n">
+        <v>7290</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="n">
         <v>499</v>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K152" t="n">
+      <c r="J152" t="n">
+        <v>497</v>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>J2K</t>
+        </is>
+      </c>
+      <c r="M152" t="n">
+        <v>497</v>
+      </c>
+      <c r="N152" t="n">
         <v>499</v>
       </c>
-      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -6372,38 +6690,40 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PETITFEE CHAMOMILE LIGHTENING HYDROGEL EYE MASK</t>
+          <t>PETITFEE B-GLUCAN DEEP FIRMING EYE MASK</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>8809508850412</t>
+          <t>8809508850504</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F153" t="n">
-        <v>6264</v>
+        <v>6842</v>
       </c>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="n">
-        <v>427</v>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K153" t="n">
-        <v>427</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="n">
+        <v>467</v>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M153" t="n">
+        <v>467</v>
+      </c>
+      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -6412,16 +6732,16 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PETITFEE COLLAGEN Q10 HYDROGEL EYE PATCH</t>
+          <t>PETITFEE BLACK PEARL &amp; GOLD HYDROGEL EYE PATCH</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>8809239800458</t>
+          <t>8809239801820</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>360</v>
+        <v>216</v>
       </c>
       <c r="F154" t="n">
         <v>5782</v>
@@ -6429,27 +6749,27 @@
       <c r="G154" t="n">
         <v>5690</v>
       </c>
-      <c r="H154" t="n">
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="n">
         <v>394</v>
       </c>
-      <c r="I154" t="n">
+      <c r="J154" t="n">
         <v>388</v>
       </c>
-      <c r="J154" t="inlineStr">
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K154" t="n">
+      <c r="M154" t="n">
         <v>388</v>
       </c>
-      <c r="L154" t="n">
-        <v>385</v>
-      </c>
+      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -6458,44 +6778,40 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PETITFEE GOLD &amp; EGF HYDROGEL EYE &amp; SPOT PATCH</t>
+          <t>PETITFEE BLACK PEARL &amp; GOLD HYDROGEL EYE PATCH 1EA</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>8809239800618</t>
+          <t>8809508850597</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>72</v>
+        <v>440</v>
       </c>
       <c r="F155" t="n">
-        <v>5782</v>
-      </c>
-      <c r="G155" t="n">
-        <v>5690</v>
-      </c>
-      <c r="H155" t="n">
-        <v>394</v>
-      </c>
+        <v>819</v>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>388</v>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>J2K</t>
-        </is>
-      </c>
-      <c r="K155" t="n">
-        <v>388</v>
-      </c>
-      <c r="L155" t="n">
-        <v>385</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M155" t="n">
+        <v>56</v>
+      </c>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -6504,44 +6820,46 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PETITFEE GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
+          <t>PETITFEE BLACK PEARL &amp; GOLD HYDROGEL MASK PACK</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>8809239802872</t>
+          <t>8809508850191</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="F156" t="n">
-        <v>6264</v>
+        <v>7035</v>
       </c>
       <c r="G156" t="n">
-        <v>6190</v>
-      </c>
-      <c r="H156" t="n">
-        <v>427</v>
-      </c>
+        <v>6990</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
-        <v>422</v>
-      </c>
-      <c r="J156" t="inlineStr">
+        <v>480</v>
+      </c>
+      <c r="J156" t="n">
+        <v>477</v>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K156" t="n">
-        <v>422</v>
-      </c>
-      <c r="L156" t="n">
-        <v>415</v>
+      <c r="M156" t="n">
+        <v>477</v>
+      </c>
+      <c r="N156" t="n">
+        <v>478</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -6550,44 +6868,40 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PETITFEE GOLD &amp; SNAIL HYDROGEL MASK PACK</t>
+          <t>PETITFEE CACAO ENERGIZING HYDROGEL EYE MASK</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>8809239802896</t>
+          <t>8809508850696</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="F157" t="n">
-        <v>7035</v>
-      </c>
-      <c r="G157" t="n">
-        <v>6990</v>
-      </c>
-      <c r="H157" t="n">
-        <v>480</v>
-      </c>
+        <v>6264</v>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
-        <v>477</v>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>J2K</t>
-        </is>
-      </c>
-      <c r="K157" t="n">
-        <v>477</v>
-      </c>
-      <c r="L157" t="n">
-        <v>478</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M157" t="n">
+        <v>427</v>
+      </c>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -6596,42 +6910,40 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PETITFEE GOLD HYDROGEL EYE PATCH</t>
+          <t>PETITFEE CACAO ENERGIZING HYDROGEL FACE MASK</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>8809239803596</t>
+          <t>8809508850689</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>360</v>
+        <v>90</v>
       </c>
       <c r="F158" t="n">
-        <v>6264</v>
-      </c>
-      <c r="G158" t="n">
-        <v>6190</v>
-      </c>
-      <c r="H158" t="n">
-        <v>427</v>
-      </c>
+        <v>7324</v>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
-        <v>422</v>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>J2K</t>
-        </is>
-      </c>
-      <c r="K158" t="n">
-        <v>422</v>
-      </c>
-      <c r="L158" t="inlineStr"/>
+        <v>499</v>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M158" t="n">
+        <v>499</v>
+      </c>
+      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -6640,38 +6952,40 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PETITFEE GOLD HYDROGEL EYE PATCH 1EA</t>
+          <t>PETITFEE CHAMOMILE LIGHTENING HYDROGEL EYE MASK</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>8809508850603</t>
+          <t>8809508850412</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>440</v>
+        <v>72</v>
       </c>
       <c r="F159" t="n">
-        <v>819</v>
+        <v>6264</v>
       </c>
       <c r="G159" t="inlineStr"/>
-      <c r="H159" t="n">
-        <v>56</v>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K159" t="n">
-        <v>56</v>
-      </c>
-      <c r="L159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="n">
+        <v>427</v>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M159" t="n">
+        <v>427</v>
+      </c>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -6680,42 +6994,46 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PETITFEE GOLD HYDROGEL MASK PACK</t>
+          <t>PETITFEE COLLAGEN Q10 HYDROGEL EYE PATCH</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>8809239803589</t>
+          <t>8809239800458</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="F160" t="n">
-        <v>7035</v>
+        <v>5782</v>
       </c>
       <c r="G160" t="n">
-        <v>6990</v>
-      </c>
-      <c r="H160" t="n">
-        <v>480</v>
-      </c>
+        <v>5690</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
-        <v>477</v>
-      </c>
-      <c r="J160" t="inlineStr">
+        <v>394</v>
+      </c>
+      <c r="J160" t="n">
+        <v>388</v>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
         <is>
           <t>J2K</t>
         </is>
       </c>
-      <c r="K160" t="n">
-        <v>477</v>
-      </c>
-      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="n">
+        <v>388</v>
+      </c>
+      <c r="N160" t="n">
+        <v>385</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -6724,110 +7042,184 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PETITFEE PINK VITA BRIGHTENING EYE MASK</t>
+          <t>PETITFEE GOLD &amp; EGF HYDROGEL EYE &amp; SPOT PATCH</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>8809508850498</t>
+          <t>8809239800618</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="F161" t="n">
-        <v>6842</v>
-      </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="n">
-        <v>467</v>
-      </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K161" t="n">
-        <v>467</v>
-      </c>
-      <c r="L161" t="inlineStr"/>
+        <v>5782</v>
+      </c>
+      <c r="G161" t="n">
+        <v>5690</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="n">
+        <v>394</v>
+      </c>
+      <c r="J161" t="n">
+        <v>388</v>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>J2K</t>
+        </is>
+      </c>
+      <c r="M161" t="n">
+        <v>388</v>
+      </c>
+      <c r="N161" t="n">
+        <v>385</v>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>PRRETI</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n"/>
-      <c r="E162" s="2" t="n"/>
-      <c r="F162" s="2" t="n"/>
-      <c r="G162" s="2" t="n"/>
-      <c r="H162" s="2" t="n"/>
-      <c r="I162" s="2" t="n"/>
-      <c r="J162" s="2" t="n"/>
-      <c r="K162" s="2" t="n"/>
-      <c r="L162" s="2" t="n"/>
+      <c r="A162" t="n">
+        <v>146</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>PETITFEE GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>8809239802872</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>72</v>
+      </c>
+      <c r="F162" t="n">
+        <v>6264</v>
+      </c>
+      <c r="G162" t="n">
+        <v>6190</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="n">
+        <v>427</v>
+      </c>
+      <c r="J162" t="n">
+        <v>422</v>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>J2K</t>
+        </is>
+      </c>
+      <c r="M162" t="n">
+        <v>422</v>
+      </c>
+      <c r="N162" t="n">
+        <v>415</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
+        <v>147</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>PETITFEE GOLD &amp; SNAIL HYDROGEL MASK PACK</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>8809239802896</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>180</v>
+      </c>
+      <c r="F163" t="n">
+        <v>7035</v>
+      </c>
+      <c r="G163" t="n">
+        <v>6990</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="n">
+        <v>480</v>
+      </c>
+      <c r="J163" t="n">
+        <v>477</v>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>J2K</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
+        <v>477</v>
+      </c>
+      <c r="N163" t="n">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
         <v>148</v>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>PRRETI</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>P/R Honey&amp;Berry Lip Sleeping Mask 15g(Tube)</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>8809411188657</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>432</v>
-      </c>
-      <c r="F163" t="n">
-        <v>1325</v>
-      </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="n">
-        <v>90</v>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K163" t="n">
-        <v>90</v>
-      </c>
-      <c r="L163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="n"/>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" s="2" t="n"/>
-      <c r="F164" s="2" t="n"/>
-      <c r="G164" s="2" t="n"/>
-      <c r="H164" s="2" t="n"/>
-      <c r="I164" s="2" t="n"/>
-      <c r="J164" s="2" t="n"/>
-      <c r="K164" s="2" t="n"/>
-      <c r="L164" s="2" t="n"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>PETITFEE</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PETITFEE GOLD HYDROGEL EYE PATCH</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>8809239803596</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>360</v>
+      </c>
+      <c r="F164" t="n">
+        <v>6264</v>
+      </c>
+      <c r="G164" t="n">
+        <v>6190</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="n">
+        <v>427</v>
+      </c>
+      <c r="J164" t="n">
+        <v>422</v>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>J2K</t>
+        </is>
+      </c>
+      <c r="M164" t="n">
+        <v>422</v>
+      </c>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -6835,41 +7227,41 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
+          <t>PETITFEE GOLD HYDROGEL EYE PATCH 1EA</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>8809738608364</t>
+          <t>8809508850603</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>690</v>
+        <v>440</v>
       </c>
       <c r="F165" t="n">
-        <v>6202</v>
+        <v>819</v>
       </c>
       <c r="G165" t="inlineStr"/>
-      <c r="H165" t="n">
-        <v>423</v>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K165" t="n">
-        <v>423</v>
-      </c>
-      <c r="L165" t="n">
-        <v>463</v>
-      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="n">
+        <v>56</v>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M165" t="n">
+        <v>56</v>
+      </c>
+      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -6877,41 +7269,45 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO TONER_200ml</t>
+          <t>PETITFEE GOLD HYDROGEL MASK PACK</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>8809657114731</t>
+          <t>8809239803589</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>90</v>
+        <v>390</v>
       </c>
       <c r="F166" t="n">
-        <v>7460</v>
-      </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="n">
-        <v>509</v>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K166" t="n">
-        <v>509</v>
-      </c>
-      <c r="L166" t="n">
-        <v>485</v>
-      </c>
+        <v>7035</v>
+      </c>
+      <c r="G166" t="n">
+        <v>6990</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="n">
+        <v>480</v>
+      </c>
+      <c r="J166" t="n">
+        <v>477</v>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>J2K</t>
+        </is>
+      </c>
+      <c r="M166" t="n">
+        <v>477</v>
+      </c>
+      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -6919,131 +7315,109 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
+          <t>PETITFEE PINK VITA BRIGHTENING EYE MASK</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>8809738600221</t>
+          <t>8809508850498</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F167" t="n">
-        <v>12641</v>
+        <v>6842</v>
       </c>
       <c r="G167" t="inlineStr"/>
-      <c r="H167" t="n">
-        <v>862</v>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K167" t="n">
-        <v>862</v>
-      </c>
-      <c r="L167" t="n">
-        <v>1093</v>
-      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="n">
+        <v>467</v>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M167" t="n">
+        <v>467</v>
+      </c>
+      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" t="n">
-        <v>152</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>ROUND LAB</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>8809738593080</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>180</v>
-      </c>
-      <c r="F168" t="n">
-        <v>6314</v>
-      </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="n">
-        <v>431</v>
-      </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K168" t="n">
-        <v>431</v>
-      </c>
-      <c r="L168" t="n">
-        <v>512</v>
-      </c>
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>PRRETI</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+      <c r="F168" s="2" t="n"/>
+      <c r="G168" s="2" t="n"/>
+      <c r="H168" s="2" t="n"/>
+      <c r="I168" s="2" t="n"/>
+      <c r="J168" s="2" t="n"/>
+      <c r="K168" s="2" t="n"/>
+      <c r="L168" s="2" t="n"/>
+      <c r="M168" s="2" t="n"/>
+      <c r="N168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PRRETI</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
+          <t>P/R Honey&amp;Berry Lip Sleeping Mask 15g(Tube)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>8809783325667</t>
+          <t>8809411188657</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>60</v>
+        <v>432</v>
       </c>
       <c r="F169" t="n">
-        <v>9753</v>
+        <v>1325</v>
       </c>
       <c r="G169" t="inlineStr"/>
-      <c r="H169" t="n">
-        <v>665</v>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K169" t="n">
-        <v>665</v>
-      </c>
-      <c r="L169" t="n">
-        <v>820</v>
-      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="n">
+        <v>90</v>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
+        <v>90</v>
+      </c>
+      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C170" s="2" t="n"/>
@@ -7056,66 +7430,104 @@
       <c r="J170" s="2" t="n"/>
       <c r="K170" s="2" t="n"/>
       <c r="L170" s="2" t="n"/>
+      <c r="M170" s="2" t="n"/>
+      <c r="N170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SKIN1004 MADAGASCAR CENTELLA AMPOULE 30ml</t>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>8809738604755</t>
+          <t>8809738608364</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>128</v>
+        <v>690</v>
       </c>
       <c r="F171" t="n">
-        <v>5038</v>
+        <v>6202</v>
       </c>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>344</v>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+        <v>6110</v>
+      </c>
+      <c r="I171" t="n">
+        <v>423</v>
+      </c>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="n">
-        <v>344</v>
-      </c>
-      <c r="L171" t="n">
-        <v>368</v>
+        <v>417</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M171" t="n">
+        <v>417</v>
+      </c>
+      <c r="N171" t="n">
+        <v>463</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n"/>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>SOME BY MI</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" s="2" t="n"/>
-      <c r="F172" s="2" t="n"/>
-      <c r="G172" s="2" t="n"/>
-      <c r="H172" s="2" t="n"/>
-      <c r="I172" s="2" t="n"/>
-      <c r="J172" s="2" t="n"/>
-      <c r="K172" s="2" t="n"/>
-      <c r="L172" s="2" t="n"/>
+      <c r="A172" t="n">
+        <v>154</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ROUND LAB 1025 DOKDO TONER_200ml</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>8809657114731</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>90</v>
+      </c>
+      <c r="F172" t="n">
+        <v>7460</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="n">
+        <v>7200</v>
+      </c>
+      <c r="I172" t="n">
+        <v>509</v>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="n">
+        <v>491</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M172" t="n">
+        <v>491</v>
+      </c>
+      <c r="N172" t="n">
+        <v>485</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -7123,107 +7535,149 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SOME BY MI AHA-BHA-PHA 30 DAYS MIRACLE CREAM [60g]</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>8809326334224</t>
+          <t>8809738600221</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F173" t="n">
-        <v>10685</v>
+        <v>12641</v>
       </c>
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>729</v>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+        <v>12480</v>
+      </c>
+      <c r="I173" t="n">
+        <v>862</v>
+      </c>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="n">
-        <v>729</v>
-      </c>
-      <c r="L173" t="n">
-        <v>1057</v>
+        <v>851</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>PAPA COSMETIC</t>
+        </is>
+      </c>
+      <c r="M173" t="n">
+        <v>851</v>
+      </c>
+      <c r="N173" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n"/>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>THE ORDINARY</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" s="2" t="n"/>
-      <c r="F174" s="2" t="n"/>
-      <c r="G174" s="2" t="n"/>
-      <c r="H174" s="2" t="n"/>
-      <c r="I174" s="2" t="n"/>
-      <c r="J174" s="2" t="n"/>
-      <c r="K174" s="2" t="n"/>
-      <c r="L174" s="2" t="n"/>
+      <c r="A174" t="n">
+        <v>156</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>ROUND LAB</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>8809738593080</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>180</v>
+      </c>
+      <c r="F174" t="n">
+        <v>6314</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="n">
+        <v>6450</v>
+      </c>
+      <c r="I174" t="n">
+        <v>431</v>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="n">
+        <v>440</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M174" t="n">
+        <v>431</v>
+      </c>
+      <c r="N174" t="n">
+        <v>512</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>THE ORDINARY</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Glycolic Acid 7% Toning Solution 240ml</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>769915234282</t>
+          <t>8809783325667</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="F175" t="n">
-        <v>12214</v>
+        <v>9753</v>
       </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>833</v>
-      </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
+        <v>9960</v>
+      </c>
+      <c r="I175" t="n">
+        <v>665</v>
+      </c>
+      <c r="J175" t="inlineStr"/>
       <c r="K175" t="n">
-        <v>833</v>
-      </c>
-      <c r="L175" t="n">
-        <v>845</v>
+        <v>679</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M175" t="n">
+        <v>665</v>
+      </c>
+      <c r="N175" t="n">
+        <v>820</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="C176" s="2" t="n"/>
@@ -7236,88 +7690,298 @@
       <c r="J176" s="2" t="n"/>
       <c r="K176" s="2" t="n"/>
       <c r="L176" s="2" t="n"/>
+      <c r="M176" s="2" t="n"/>
+      <c r="N176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>VT COSMETICS</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>VT PDRN ESSENCE 100</t>
+          <t>SKIN1004 MADAGASCAR CENTELLA AMPOULE 30ml</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>8803463004286</t>
+          <t>8809738604755</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F177" t="n">
-        <v>19080</v>
+        <v>5038</v>
       </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I177" t="n">
+        <v>344</v>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="n">
+        <v>389</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M177" t="n">
+        <v>344</v>
+      </c>
+      <c r="N177" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" s="2" t="n"/>
+      <c r="F178" s="2" t="n"/>
+      <c r="G178" s="2" t="n"/>
+      <c r="H178" s="2" t="n"/>
+      <c r="I178" s="2" t="n"/>
+      <c r="J178" s="2" t="n"/>
+      <c r="K178" s="2" t="n"/>
+      <c r="L178" s="2" t="n"/>
+      <c r="M178" s="2" t="n"/>
+      <c r="N178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>159</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SOME BY MI</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SOME BY MI AHA-BHA-PHA 30 DAYS MIRACLE CREAM [60g]</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>8809326334224</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>100</v>
+      </c>
+      <c r="F179" t="n">
+        <v>10685</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="n">
+        <v>729</v>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M179" t="n">
+        <v>729</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="2" t="n"/>
+      <c r="I180" s="2" t="n"/>
+      <c r="J180" s="2" t="n"/>
+      <c r="K180" s="2" t="n"/>
+      <c r="L180" s="2" t="n"/>
+      <c r="M180" s="2" t="n"/>
+      <c r="N180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>160</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>THE ORDINARY</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Glycolic Acid 7% Toning Solution 240ml</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>769915234282</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>108</v>
+      </c>
+      <c r="F181" t="n">
+        <v>12214</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="n">
+        <v>833</v>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M181" t="n">
+        <v>833</v>
+      </c>
+      <c r="N181" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="2" t="n"/>
+      <c r="G182" s="2" t="n"/>
+      <c r="H182" s="2" t="n"/>
+      <c r="I182" s="2" t="n"/>
+      <c r="J182" s="2" t="n"/>
+      <c r="K182" s="2" t="n"/>
+      <c r="L182" s="2" t="n"/>
+      <c r="M182" s="2" t="n"/>
+      <c r="N182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>161</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>VT COSMETICS</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>VT PDRN ESSENCE 100</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>8803463004286</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>120</v>
+      </c>
+      <c r="F183" t="n">
+        <v>19080</v>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="n">
+        <v>20700</v>
+      </c>
+      <c r="I183" t="n">
         <v>1301</v>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K177" t="n">
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="n">
+        <v>1412</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M183" t="n">
         <v>1301</v>
       </c>
-      <c r="L177" t="n">
+      <c r="N183" t="n">
         <v>1336</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>158</v>
-      </c>
-      <c r="B178" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="n">
+        <v>162</v>
+      </c>
+      <c r="B184" t="inlineStr">
         <is>
           <t>VT COSMETICS</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>VT REEDLE SHOT 100</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>8809695678363</t>
         </is>
       </c>
-      <c r="E178" t="n">
+      <c r="E184" t="n">
         <v>96</v>
       </c>
-      <c r="F178" t="n">
+      <c r="F184" t="n">
         <v>13568</v>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="n">
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="n">
+        <v>14720</v>
+      </c>
+      <c r="I184" t="n">
         <v>925</v>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>FINESKIN</t>
-        </is>
-      </c>
-      <c r="K178" t="n">
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="n">
+        <v>1004</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>FINESKIN</t>
+        </is>
+      </c>
+      <c r="M184" t="n">
         <v>925</v>
       </c>
-      <c r="L178" t="n">
+      <c r="N184" t="n">
         <v>974</v>
       </c>
     </row>
